--- a/public/downloads/goldfin-cash-basis-p-l-review-sample.xlsx
+++ b/public/downloads/goldfin-cash-basis-p-l-review-sample.xlsx
@@ -18,8 +18,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0;[Red]($#,##0);-"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; mo&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0"/>
   </numFmts>
   <fonts count="6">
@@ -189,7 +189,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -212,7 +212,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="8">
@@ -222,7 +222,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="9">
@@ -232,7 +232,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="10">
@@ -242,7 +242,7 @@
         </is>
       </c>
       <c r="B10" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="11">
@@ -313,7 +313,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15 to 2026-05-31</t>
+          <t>2026-05-01 to 2026-05-31</t>
         </is>
       </c>
     </row>
@@ -344,7 +344,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="7">
@@ -354,7 +354,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>-41180</v>
+        <v>-71900</v>
       </c>
     </row>
     <row r="8">
@@ -364,7 +364,7 @@
         </is>
       </c>
       <c r="B8" s="9">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="9">
@@ -391,7 +391,7 @@
         </is>
       </c>
       <c r="B11" s="13">
-        <v>14600</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="12">
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="B12" s="13">
-        <v>7845</v>
+        <v>14460</v>
       </c>
     </row>
     <row r="13">
@@ -411,7 +411,7 @@
         </is>
       </c>
       <c r="B13" s="13">
-        <v>49520</v>
+        <v>292500</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +541,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-01</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B4" s="8">
-        <v>38400</v>
+        <v>268000</v>
       </c>
     </row>
     <row r="5">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B5" s="8">
-        <v>52300</v>
+        <v>96400</v>
       </c>
     </row>
     <row r="6">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B6" s="8">
-        <v>41180</v>
+        <v>71900</v>
       </c>
     </row>
     <row r="7">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="8">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <v>6800</v>
+        <v>72948</v>
       </c>
     </row>
     <row r="9">
@@ -613,8 +613,8 @@
           <t>runwayMonths</t>
         </is>
       </c>
-      <c r="B9" s="8">
-        <v>5.6</v>
+      <c r="B9" s="11">
+        <v>3.67</v>
       </c>
     </row>
     <row r="10">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <v>14600</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
           <t>revenueVsPriorPct</t>
         </is>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="10">
         <v>6.4</v>
       </c>
     </row>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <v>11120</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="13">
@@ -653,7 +653,7 @@
           <t>profitVsPriorPct</t>
         </is>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="10">
         <v>3.1</v>
       </c>
     </row>
@@ -673,7 +673,7 @@
           <t>coveragePct</t>
         </is>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="10">
         <v>94</v>
       </c>
     </row>
@@ -683,7 +683,7 @@
           <t>transactionsCount</t>
         </is>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="12">
         <v>118</v>
       </c>
     </row>
@@ -693,7 +693,7 @@
           <t>reserve_floor_months</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="12">
         <v>3</v>
       </c>
     </row>
@@ -711,7 +711,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Detail</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -723,12 +723,12 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>Not embedded</t>
+          <t>Transaction detail</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>The current frontend report snapshot does not include raw transaction rows. Server-side XLSX generation can populate this sheet from the transactions table.</t>
+          <t>This planning workbook summarizes your connected bank and card activity. Line-item transaction detail lives in your GoldFin Desk account and your own bank export.</t>
         </is>
       </c>
     </row>

--- a/public/downloads/goldfin-cash-basis-p-l-review-sample.xlsx
+++ b/public/downloads/goldfin-cash-basis-p-l-review-sample.xlsx
@@ -217,7 +217,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Sample figures</t>
+          <t>Sample figures (pre-filled - type over them)</t>
         </is>
       </c>
     </row>
@@ -251,16 +251,36 @@
         <v>71900</v>
       </c>
     </row>
-    <row r="14"/>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Profit this month</t>
+        </is>
+      </c>
+      <c r="B14" s="8">
+        <v>24500</v>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>Prefer it filled from your bank every month? That is GoldFin Reports - goldfindesk.com/pricing</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>A planning artifact, not tax, accounting, credit, legal, or investment advice.</t>
         </is>
@@ -273,8 +293,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -313,14 +334,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Your inputs</t>
+          <t>Revenue &amp; assumptions</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Deposits (money in)</t>
+          <t>Revenue (deposits / money in)</t>
         </is>
       </c>
       <c r="B7" s="14">
@@ -330,62 +351,201 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Operating cash out</t>
-        </is>
-      </c>
-      <c r="B8" s="14">
-        <v>71900</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
           <t>Tax reserve rate (%)</t>
         </is>
       </c>
-      <c r="B9" s="16">
+      <c r="B8" s="16">
         <v>15</v>
       </c>
     </row>
-    <row r="10"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Where the money went (edit these)</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Results</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>% of revenue</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Cash profit proxy</t>
-        </is>
-      </c>
-      <c r="B12" s="9">
-        <f>$B$7-$B$8</f>
-        <v>24500</v>
+          <t>Materials / cost of goods</t>
+        </is>
+      </c>
+      <c r="B12" s="14">
+        <v>15000</v>
+      </c>
+      <c r="C12" s="10">
+        <f>IF($B$7=0,0,B12/$B$7*100)</f>
+        <v>15.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Tax reserve target</t>
-        </is>
-      </c>
-      <c r="B13" s="8">
-        <f>$B$7*$B$9/100</f>
-        <v>14460</v>
+          <t>Payroll &amp; contractors</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <v>30000</v>
+      </c>
+      <c r="C13" s="10">
+        <f>IF($B$7=0,0,B13/$B$7*100)</f>
+        <v>31.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>After-tax cash proxy</t>
-        </is>
-      </c>
-      <c r="B14" s="9">
-        <f>($B$7-$B$8)-$B$7*$B$9/100</f>
-        <v>10040</v>
+          <t>Rent &amp; utilities</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <v>6000</v>
+      </c>
+      <c r="C14" s="10">
+        <f>IF($B$7=0,0,B14/$B$7*100)</f>
+        <v>6.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Software &amp; subscriptions</t>
+        </is>
+      </c>
+      <c r="B15" s="14">
+        <v>4500</v>
+      </c>
+      <c r="C15" s="10">
+        <f>IF($B$7=0,0,B15/$B$7*100)</f>
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Marketing &amp; sales</t>
+        </is>
+      </c>
+      <c r="B16" s="14">
+        <v>5400</v>
+      </c>
+      <c r="C16" s="10">
+        <f>IF($B$7=0,0,B16/$B$7*100)</f>
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Owner pay</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <v>8000</v>
+      </c>
+      <c r="C17" s="10">
+        <f>IF($B$7=0,0,B17/$B$7*100)</f>
+        <v>8.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B18" s="14">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="10">
+        <f>IF($B$7=0,0,B18/$B$7*100)</f>
+        <v>3.11</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Total spending</t>
+        </is>
+      </c>
+      <c r="B19" s="9">
+        <f>SUM(B12:B18)</f>
+        <v>71900</v>
+      </c>
+      <c r="C19" s="10">
+        <f>IF($B$7=0,0,B19/$B$7*100)</f>
+        <v>74.59</v>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Operating profit</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>$B$7-B19</f>
+        <v>24500</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Profit margin</t>
+        </is>
+      </c>
+      <c r="B23" s="10">
+        <f>IF($B$7=0,0,($B$7-B19)/$B$7*100)</f>
+        <v>25.41</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Tax reserve target</t>
+        </is>
+      </c>
+      <c r="B24" s="8">
+        <f>($B$7-B19)*$B$8/100</f>
+        <v>3675</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Cash left after tax reserve</t>
+        </is>
+      </c>
+      <c r="B25" s="9">
+        <f>($B$7-B19)-($B$7-B19)*$B$8/100</f>
+        <v>20825</v>
       </c>
     </row>
   </sheetData>
